--- a/examples/validation_results/validation_frame_fab_error.xlsx
+++ b/examples/validation_results/validation_frame_fab_error.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Node Displacements" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Maximum Displacement Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Reaction Forces" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Member Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Member Full Results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Frame Member Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Frame Member Full Results" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1345,32 +1345,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fx ()</t>
+          <t>Fx (KN)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Fy ()</t>
+          <t>Fy (KN)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fz ()</t>
+          <t>Fz (KN)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mx (·)</t>
+          <t>Mx (KN*M)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>My (·)</t>
+          <t>My (KN*M)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mz (·)</t>
+          <t>Mz (KN*M)</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,12 +1518,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>N_tension (+) (KN)</t>
+          <t>N (KN)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sigma (KN/M^2)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_i (KN)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_i (KN)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_i (KN)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>My_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_j (KN)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_j (KN)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_j (KN)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_j (KN*M)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>My_j (KN*M)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_j (KN*M)</t>
         </is>
       </c>
     </row>
@@ -1557,6 +1617,42 @@
       <c r="I2" t="n">
         <v>6.476308181589739</v>
       </c>
+      <c r="J2" t="n">
+        <v>-0.03069770078073537</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-1.056826096416637e-13</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.311312169960388e-13</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.448418222140104e-16</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1227908031186297</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-4.296386158179834e-13</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.03069770078073537</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.056826096416637e-13</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-1.311312169960388e-13</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-6.448418222140104e-16</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.1227908031194165</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-2.044570420319988e-13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1588,6 +1684,42 @@
       <c r="I3" t="n">
         <v>6.476308181694269</v>
       </c>
+      <c r="J3" t="n">
+        <v>-0.03069770078123084</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1.056301890213897e-13</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.441136264825673e-13</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.44768254624497e-16</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1227908031177474</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-4.295338792934306e-13</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.03069770078123084</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.056301890213897e-13</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-3.441136264825673e-13</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-6.44768254624497e-16</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.1227908031198122</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-2.042472548349078e-13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1619,6 +1751,42 @@
       <c r="I4" t="n">
         <v>-6.476308181698468</v>
       </c>
+      <c r="J4" t="n">
+        <v>0.03069770078125075</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.060312698528079e-13</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.440719931191438e-13</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6.447799049403346e-16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1227908031177475</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.31381983041816e-13</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.03069770078125075</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.060312698528079e-13</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-3.440719931191438e-13</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-6.447799049403346e-16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.122790803119812</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.048056360750312e-13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1650,6 +1818,42 @@
       <c r="I5" t="n">
         <v>-6.4763081816888</v>
       </c>
+      <c r="J5" t="n">
+        <v>0.03069770078120492</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.06028662285421e-13</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.312283615106935e-13</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.4461311945537e-16</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1227908031186295</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.313767609041526e-13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.03069770078120492</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.06028662285421e-13</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1.312283615106935e-13</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-6.4461311945537e-16</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.1227908031194169</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.04795212808373e-13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1681,6 +1885,42 @@
       <c r="I6" t="n">
         <v>-333297.705107439</v>
       </c>
+      <c r="J6" t="n">
+        <v>-0.1688777907386338</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.016589946586002e-13</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.297850715786808e-13</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.003947125286698e-15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6755111629518569</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-3.043623884663222e-13</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1688777907386338</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.016589946586002e-13</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1.297850715786808e-13</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1.003947125286698e-15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.6755111629526356</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-3.055915794852785e-13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1712,6 +1952,42 @@
       <c r="I7" t="n">
         <v>-333297.7051074389</v>
       </c>
+      <c r="J7" t="n">
+        <v>-0.1688777907390886</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1.016964272859168e-13</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.533839887381873e-13</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.003662332591825e-15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6755111629511585</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-3.043323765989816e-13</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1688777907390886</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.016964272859168e-13</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-3.533839887381873e-13</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.003662332591825e-15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.6755111629532795</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-3.058461871165189e-13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1743,6 +2019,42 @@
       <c r="I8" t="n">
         <v>-35.62822589434915</v>
       </c>
+      <c r="J8" t="n">
+        <v>0.168877790739215</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.020563685019457e-13</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.534950110406498e-13</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.004399389143434e-15</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6755111629511581</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.057675499107009e-13</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.168877790739215</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.020563685019457e-13</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-3.534950110406498e-13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.004399389143434e-15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.6755111629532804</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.065706611009732e-13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1774,6 +2086,42 @@
       <c r="I9" t="n">
         <v>-35.62822589434336</v>
       </c>
+      <c r="J9" t="n">
+        <v>0.1688777907391875</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.020658017410055e-13</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.294520046712933e-13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.00316870126798e-15</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6755111629518573</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.057815917171203e-13</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.1688777907391875</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.020658017410055e-13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-1.294520046712933e-13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.00316870126798e-15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.6755111629526342</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.06613218728913e-13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1805,6 +2153,42 @@
       <c r="I10" t="n">
         <v>5.612952057714819</v>
       </c>
+      <c r="J10" t="n">
+        <v>-0.02660539275348128</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-8.004421522552583e-14</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.729727472365994e-13</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.564708730707019e-16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1064215710118925</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2.018431888207753e-13</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.02660539275348128</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.004421522552583e-14</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.729727472365994e-13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-8.564708730707019e-16</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.1064215710129304</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-2.784221025323803e-13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +2220,42 @@
       <c r="I11" t="n">
         <v>5.612952057830467</v>
       </c>
+      <c r="J11" t="n">
+        <v>-0.0266053927541634</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-8.013368217045158e-14</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.987921104453562e-13</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8.550105194513328e-16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1064215710113263</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-2.022001209684786e-13</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0266053927541634</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.013368217045158e-14</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-3.987921104453562e-13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-8.550105194513328e-16</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.1064215710137209</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-2.786019720542305e-13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +2287,42 @@
       <c r="I12" t="n">
         <v>-5.612952057774971</v>
       </c>
+      <c r="J12" t="n">
+        <v>0.02660539275385337</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.020341599304231e-14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.983480212355062e-13</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8.557517805408608e-16</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1064215710113285</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.022708440431196e-13</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.02660539275385337</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-8.020341599304231e-14</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-3.983480212355062e-13</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-8.557517805408608e-16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.1064215710137182</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.789496519151347e-13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +2354,42 @@
       <c r="I13" t="n">
         <v>-5.612952057779497</v>
       </c>
+      <c r="J13" t="n">
+        <v>0.02660539275387483</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.017778624435488e-14</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.73749903353837e-13</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8.569012298343786e-16</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.106421571011891</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.022430901330703e-13</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.02660539275387483</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-8.017778624435488e-14</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.73749903353837e-13</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-8.569012298343786e-16</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.1064215710129344</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.788236273330586e-13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1929,6 +2421,42 @@
       <c r="I14" t="n">
         <v>0.8633561238031532</v>
       </c>
+      <c r="J14" t="n">
+        <v>-0.004092308026883984</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-3.362018027011895e-14</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.466116282879739e-13</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.51193307424836e-16</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.01636923210568808</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-5.810951370820892e-14</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.004092308026883984</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.362018027011895e-14</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-3.466116282879739e-13</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-3.51193307424836e-16</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.01636923210776953</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.436115679125046e-13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1960,6 +2488,42 @@
       <c r="I15" t="n">
         <v>0.8633561238031532</v>
       </c>
+      <c r="J15" t="n">
+        <v>-0.004092308026883984</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-3.35688615624581e-14</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.634870182622763e-13</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.582742029919923e-16</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.01636923210576091</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-5.801105008639339e-14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.004092308026883984</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.35688615624581e-14</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-3.634870182622763e-13</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-3.582742029919923e-16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.01636923210794006</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.434021192883554e-13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1991,6 +2555,42 @@
       <c r="I16" t="n">
         <v>-0.8633561238286983</v>
       </c>
+      <c r="J16" t="n">
+        <v>0.004092308026948044</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.32663270766845e-14</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.629319067499637e-13</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.536236808885884e-16</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.01636923210576025</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.70921169700583e-14</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.004092308026948044</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-3.32663270766845e-14</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-3.629319067499637e-13</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-3.536236808885884e-16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.01636923210793961</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.425058454900481e-13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2022,6 +2622,42 @@
       <c r="I17" t="n">
         <v>-0.8633561238354956</v>
       </c>
+      <c r="J17" t="n">
+        <v>0.00409230802698024</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.341636523803729e-14</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3.465006059855114e-13</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.547861404194171e-16</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.01636923210568919</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5.73153777575905e-14</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.00409230802698024</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-3.341636523803729e-14</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-3.465006059855114e-13</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-3.547861404194171e-16</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.01636923210776908</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.431828136706332e-13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2053,6 +2689,42 @@
       <c r="I18" t="n">
         <v>1.061310761179206e-14</v>
       </c>
+      <c r="J18" t="n">
+        <v>-5.030613008684149e-17</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.885780586188048e-15</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.270205090833757e-13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-7.01804066249867e-16</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.0804263836559e-13</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.551536676913656e-14</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.030613008684149e-17</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-3.885780586188048e-15</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.270205090833757e-13</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7.01804066249867e-16</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5.081214343014151e-13</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.554312234475219e-14</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2084,6 +2756,42 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-3.986894838778718e-15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1381800899578367</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-6.517254395557321e-16</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.5527203598313468</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.594530754352647e-14</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.986894838778718e-15</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.1381800899578367</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6.517254395557321e-16</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.5527203598313467</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.594985116670313e-14</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2115,6 +2823,42 @@
       <c r="I20" t="n">
         <v>-7.09752316480593e-16</v>
       </c>
+      <c r="J20" t="n">
+        <v>3.364225984971083e-18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.934352843515398e-15</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1.274808412077357e-13</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-7.022919572274855e-16</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.099214167321203e-13</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.568190022283034e-14</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-3.364225984971083e-18</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-3.934352843515398e-15</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.274808412077357e-13</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7.022919572274855e-16</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.099253264822925e-13</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.576516694967722e-14</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2146,6 +2890,42 @@
       <c r="I21" t="n">
         <v>-2.710505431213761e-12</v>
       </c>
+      <c r="J21" t="n">
+        <v>1.4210854715202e-14</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.973308852973428e-15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1381800899581102</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-6.515814257910062e-16</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.5527203598324407</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.584863837395873e-14</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1.4210854715202e-14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-3.973308852973428e-15</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.1381800899581102</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6.515814257910062e-16</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.5527203598324405</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.593783244982845e-14</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2177,6 +2957,42 @@
       <c r="I22" t="n">
         <v>2.820269181907326e-14</v>
       </c>
+      <c r="J22" t="n">
+        <v>-1.336807591937417e-16</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.142730437526552e-14</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-1.266629055343862e-13</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-7.80191883320569e-16</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.062255883614868e-13</v>
+      </c>
+      <c r="O22" t="n">
+        <v>8.570921750106208e-14</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.336807591937417e-16</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.142730437526552e-14</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.266629055343862e-13</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7.80191883320569e-16</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5.061894774939023e-13</v>
+      </c>
+      <c r="U22" t="n">
+        <v>8.570921750106208e-14</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2208,6 +3024,42 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-2.156674552224533e-14</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.1422723979854889</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-6.483837255540837e-16</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.5690895919419561</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-8.612098424982906e-14</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.156674552224533e-14</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.1422723979854889</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6.483837255540837e-16</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5690895919419559</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-8.641297992813301e-14</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2239,6 +3091,42 @@
       <c r="I24" t="n">
         <v>3.744470319065365e-14</v>
       </c>
+      <c r="J24" t="n">
+        <v>-1.774878931412836e-16</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.148281552649678e-14</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.270391248829942e-13</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-7.784571598445922e-16</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.081653015142231e-13</v>
+      </c>
+      <c r="O24" t="n">
+        <v>8.570921750106208e-14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.774878931412836e-16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.148281552649678e-14</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.270391248829942e-13</v>
+      </c>
+      <c r="S24" t="n">
+        <v>7.784571598445922e-16</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5.081478059699478e-13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8.615330671091215e-14</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2270,6 +3158,42 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.141473676500339e-14</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.1422723979851855</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-6.486090920928102e-16</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.5690895919407426</v>
+      </c>
+      <c r="O25" t="n">
+        <v>8.54625573384283e-14</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.141473676500339e-14</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.1422723979851855</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6.486090920928102e-16</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5690895919407422</v>
+      </c>
+      <c r="U25" t="n">
+        <v>8.585533678159801e-14</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2301,6 +3225,42 @@
       <c r="I26" t="n">
         <v>-1.309765167015322e-13</v>
       </c>
+      <c r="J26" t="n">
+        <v>6.208286892050575e-16</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.729550084903167e-14</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-8.408064744864054e-14</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-4.566659550508945e-16</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.361255407452572e-13</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.891820033961267e-13</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-6.208286892050575e-16</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-4.729550084903167e-14</v>
+      </c>
+      <c r="R26" t="n">
+        <v>8.408064744864054e-14</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.566659550508945e-16</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.356314604241669e-13</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.891820033961267e-13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2332,6 +3292,42 @@
       <c r="I27" t="n">
         <v>-4.336808689942018e-11</v>
       </c>
+      <c r="J27" t="n">
+        <v>2.273736754432321e-13</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-4.676173038271414e-14</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.02251308472698921</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-4.275943135957665e-16</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.09005233890795705</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.867563777792461e-13</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-2.273736754432321e-13</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.676173038271414e-14</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.02251308472698921</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.275943135957665e-16</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.09005233890795727</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-1.87337465282466e-13</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2363,6 +3359,42 @@
       <c r="I28" t="n">
         <v>5.679214913363221e-14</v>
       </c>
+      <c r="J28" t="n">
+        <v>-2.691947868883633e-16</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.662936703425657e-14</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-8.392083454423743e-14</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-4.597017211338539e-16</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.356551736916173e-13</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.865174681370263e-13</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.691947868883633e-16</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-4.662936703425657e-14</v>
+      </c>
+      <c r="R28" t="n">
+        <v>8.392083454423743e-14</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.597017211338539e-16</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.357113942420649e-13</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.865174681370263e-13</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2394,6 +3426,42 @@
       <c r="I29" t="n">
         <v>4.336808689942018e-11</v>
       </c>
+      <c r="J29" t="n">
+        <v>-2.273736754432321e-13</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.699066218428263e-14</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.02251308472681168</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-4.277060378933975e-16</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.09005233890724629</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.878501785844625e-13</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.273736754432321e-13</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-4.699066218428263e-14</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.02251308472681168</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.277060378933975e-16</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.09005233890724762</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.880751188897983e-13</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2425,6 +3493,42 @@
       <c r="I30" t="n">
         <v>3.80363194056146e-14</v>
       </c>
+      <c r="J30" t="n">
+        <v>-1.802921540148587e-16</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.308464613382966e-14</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-3.586154729876037e-14</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1.071191746415678e-16</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.432963679872677e-13</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.323385845353187e-13</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.802921540148587e-16</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-3.308464613382966e-14</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.586154729876037e-14</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.071191746415678e-16</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.435960104028153e-13</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.314504061156185e-13</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2456,6 +3560,42 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-3.363850098582328e-14</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.004092308026984459</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-1.812412399583363e-16</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.01636923210793761</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-1.351703120018463e-13</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.363850098582328e-14</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.004092308026984459</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.812412399583363e-16</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.01636923210793872</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-1.339376958847387e-13</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2487,6 +3627,42 @@
       <c r="I32" t="n">
         <v>-1.316763312145694e-13</v>
       </c>
+      <c r="J32" t="n">
+        <v>6.241458099166313e-16</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.352873534367973e-14</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-3.572678161051504e-14</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1.101549407245273e-16</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.430490993232485e-13</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.341149413747189e-13</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-6.241458099166313e-16</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-3.352873534367973e-14</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.572678161051504e-14</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.101549407245273e-16</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.427650451406545e-13</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.341149413747189e-13</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2517,6 +3693,42 @@
       </c>
       <c r="I33" t="n">
         <v>-8.673617379884035e-11</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.300334953305864e-14</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.004092308026943159</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-1.805385040703131e-16</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.0163692321077733</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.326015304135093e-13</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-4.547473508864641e-13</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-3.300334953305864e-14</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.004092308026943159</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.805385040703131e-16</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.01636923210777352</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.314252658509586e-13</v>
       </c>
     </row>
   </sheetData>
@@ -2530,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP33"/>
+  <dimension ref="A1:AS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2541,205 +3753,220 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>i</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>L (M)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>N_tension (+) (KN)</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Δu_local_x (M)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>axial strain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>N (KN)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>sigma (KN/M^2)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>u_g_1 (M)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>u_g_2 (M)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>u_g_3 (M)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>u_g_4 (rad)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>u_g_5 (rad)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>u_g_6 (rad)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>u_g_7 (M)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>u_g_8 (M)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>u_g_9 (M)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>u_g_10 (rad)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>u_g_11 (rad)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>u_g_12 (rad)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>u_l_1 (M)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>u_l_2 (M)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>u_l_3 (M)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>u_l_4 (rad)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>u_l_5 (rad)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>u_l_6 (rad)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>u_l_7 (M)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>u_l_8 (M)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>u_l_9 (M)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>u_l_10 (rad)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>u_l_11 (rad)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>u_l_12 (rad)</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>q_l_1 (KN)</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>q_l_2 (KN)</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>q_l_3 (KN)</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>q_l_4 (KN*M)</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>q_l_5 (KN*M)</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>q_l_6 (KN*M)</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>q_l_7 (KN)</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>q_l_8 (KN)</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>q_l_9 (KN)</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>q_l_10 (KN*M)</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>q_l_11 (KN*M)</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>q_l_12 (KN*M)</t>
         </is>
@@ -2749,30 +3976,32 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>1.942892454476922e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.23815409079487e-08</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.03069770078073537</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>6.476308181589739</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -2783,32 +4012,32 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>-0.000497800553184697</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>8.848921481134703e-16</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>1.942892454476922e-07</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>-1.521497120175572e-16</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>-0.0001659335177284096</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>-2.265660456427604e-16</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -2819,57 +4048,66 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.942892454476922e-07</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>8.848921481134703e-16</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>0.000497800553184697</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>-2.265660456427604e-16</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AF2" t="n">
         <v>-0.0001659335177284096</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>1.521497120175572e-16</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>-0.03069770078073537</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>-1.056826096416637e-13</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>1.311312169960388e-13</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>6.448418222140104e-16</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>0.1227908031186297</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>-4.296386158179834e-13</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>0.03069770078073537</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AO2" t="n">
         <v>1.056826096416637e-13</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AP2" t="n">
         <v>-1.311312169960388e-13</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AQ2" t="n">
         <v>-6.448418222140104e-16</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AR2" t="n">
         <v>-0.1227908031194165</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AS2" t="n">
         <v>-2.044570420319988e-13</v>
       </c>
     </row>
@@ -2877,30 +4115,32 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.942892454508281e-07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.238154090847134e-08</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.03069770078123083</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>6.476308181694269</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -2911,32 +4151,32 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>8.848925726377748e-16</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>1.942892454508281e-07</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>-1.522206922017046e-16</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>-0.0001659335177280808</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>-2.265401975707692e-16</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
@@ -2947,57 +4187,66 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.942892454508281e-07</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>8.848925726377748e-16</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>0.0004978005531828473</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>-2.265401975707692e-16</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AF3" t="n">
         <v>-0.0001659335177280808</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>1.522206922017046e-16</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>-0.03069770078123084</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>-1.056301890213897e-13</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>3.441136264825673e-13</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>6.44768254624497e-16</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>0.1227908031177474</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AM3" t="n">
         <v>-4.295338792934306e-13</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AN3" t="n">
         <v>0.03069770078123084</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AO3" t="n">
         <v>1.056301890213897e-13</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AP3" t="n">
         <v>-3.441136264825673e-13</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AQ3" t="n">
         <v>-6.44768254624497e-16</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AR3" t="n">
         <v>-0.1227908031198122</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AS3" t="n">
         <v>-2.042472548349078e-13</v>
       </c>
     </row>
@@ -3005,30 +4254,32 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>-1.942892454509541e-07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-3.238154090849235e-08</v>
+      </c>
+      <c r="H4" t="n">
         <v>-0.03069770078125074</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>-6.476308181698468</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -3039,32 +4290,32 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>-8.891328783900011e-16</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>-1.942892454509541e-07</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>1.530921263289087e-16</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>-0.0001659335177280807</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>-2.265442909249824e-16</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
@@ -3075,57 +4326,66 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>-1.942892454509541e-07</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>-8.891328783900011e-16</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
         <v>0.0004978005531828473</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>-2.265442909249824e-16</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
         <v>-0.0001659335177280807</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>-1.530921263289087e-16</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>0.03069770078125075</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
         <v>1.060312698528079e-13</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AJ4" t="n">
         <v>3.440719931191438e-13</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AK4" t="n">
         <v>6.447799049403346e-16</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AL4" t="n">
         <v>0.1227908031177475</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AM4" t="n">
         <v>4.31381983041816e-13</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AN4" t="n">
         <v>-0.03069770078125075</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AO4" t="n">
         <v>-1.060312698528079e-13</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AP4" t="n">
         <v>-3.440719931191438e-13</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AQ4" t="n">
         <v>-6.447799049403346e-16</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AR4" t="n">
         <v>-0.122790803119812</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AS4" t="n">
         <v>2.048056360750312e-13</v>
       </c>
     </row>
@@ -3133,30 +4393,32 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>-1.94289245450664e-07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-3.2381540908444e-08</v>
+      </c>
+      <c r="H5" t="n">
         <v>-0.03069770078120491</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>-6.4763081816888</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -3167,32 +4429,32 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>-0.0004978005531846971</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>-8.891328499999085e-16</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>-1.94289245450664e-07</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>1.530956406052565e-16</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>-0.0001659335177284097</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>-2.264856906194544e-16</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
@@ -3203,57 +4465,66 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>-1.94289245450664e-07</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>-8.891328499999085e-16</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
         <v>0.0004978005531846971</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>-2.264856906194544e-16</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
         <v>-0.0001659335177284097</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AG5" t="n">
         <v>-1.530956406052565e-16</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
         <v>0.03069770078120492</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
         <v>1.06028662285421e-13</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AJ5" t="n">
         <v>1.312283615106935e-13</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AK5" t="n">
         <v>6.4461311945537e-16</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AL5" t="n">
         <v>0.1227908031186295</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AM5" t="n">
         <v>4.313767609041526e-13</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AN5" t="n">
         <v>-0.03069770078120492</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AO5" t="n">
         <v>-1.06028662285421e-13</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AP5" t="n">
         <v>-1.312283615106935e-13</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AQ5" t="n">
         <v>-6.4461311945537e-16</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AR5" t="n">
         <v>-0.1227908031194169</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AS5" t="n">
         <v>2.04795212808373e-13</v>
       </c>
     </row>
@@ -3261,127 +4532,138 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>9</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>-0.009998931153223171</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.001666488525537195</v>
+      </c>
+      <c r="H6" t="n">
         <v>-1579.831122209261</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>-333297.705107439</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>-0.000497800553184697</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>8.848921481134703e-16</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>1.942892454476922e-07</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>-1.521497120175572e-16</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>-0.0001659335177284096</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>-2.265660456427604e-16</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>2.207429876228768e-15</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>-0.009998736863977724</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>-1.513191775452895e-16</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>-5.793042247975463e-16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>1.942892454476922e-07</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>8.848921481134703e-16</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>0.000497800553184697</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>-2.265660456427604e-16</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>-0.0001659335177284096</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>1.521497120175572e-16</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>-0.009998736863977724</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>2.207429876228768e-15</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AD6" t="n">
         <v>0.00423196042827995</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>-5.793042247975463e-16</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AF6" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AG6" t="n">
         <v>1.513191775452895e-16</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AH6" t="n">
         <v>-0.1688777907386338</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AI6" t="n">
         <v>-1.016589946586002e-13</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AJ6" t="n">
         <v>1.297850715786808e-13</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AK6" t="n">
         <v>1.003947125286698e-15</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AL6" t="n">
         <v>0.6755111629518569</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AM6" t="n">
         <v>-3.043623884663222e-13</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AN6" t="n">
         <v>0.1688777907386338</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AO6" t="n">
         <v>1.016589946586002e-13</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AP6" t="n">
         <v>-1.297850715786808e-13</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AQ6" t="n">
         <v>-1.003947125286698e-15</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AR6" t="n">
         <v>-0.6755111629526356</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AS6" t="n">
         <v>-3.055915794852785e-13</v>
       </c>
     </row>
@@ -3389,127 +4671,138 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
+        <v>-0.009998931153223168</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.001666488525537195</v>
+      </c>
+      <c r="H7" t="n">
         <v>-1579.83112220926</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>-333297.7051074389</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>8.848925726377748e-16</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>1.942892454508281e-07</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>-1.522206922017046e-16</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>-0.0001659335177280808</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>-2.265401975707692e-16</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>2.20743100433644e-15</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>-0.009998736863977717</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>-1.511978472574226e-16</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>-5.791783144273565e-16</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>1.942892454508281e-07</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>8.848925726377748e-16</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>0.0004978005531828473</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>-2.265401975707692e-16</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>-0.0001659335177280808</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>1.522206922017046e-16</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>-0.009998736863977717</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
         <v>2.20743100433644e-15</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
         <v>0.004231960428275111</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>-5.791783144273565e-16</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AF7" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
         <v>1.511978472574226e-16</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
         <v>-0.1688777907390886</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
         <v>-1.016964272859168e-13</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AJ7" t="n">
         <v>3.533839887381873e-13</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AK7" t="n">
         <v>1.003662332591825e-15</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AL7" t="n">
         <v>0.6755111629511585</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AM7" t="n">
         <v>-3.043323765989816e-13</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AN7" t="n">
         <v>0.1688777907390886</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AO7" t="n">
         <v>1.016964272859168e-13</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AP7" t="n">
         <v>-3.533839887381873e-13</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AQ7" t="n">
         <v>-1.003662332591825e-15</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AR7" t="n">
         <v>-0.6755111629532795</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AS7" t="n">
         <v>-3.058461871165189e-13</v>
       </c>
     </row>
@@ -3517,127 +4810,138 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>11</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>-1.068846776830474e-06</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.781411294717457e-07</v>
+      </c>
+      <c r="H8" t="n">
         <v>-0.168877790739215</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>-35.62822589434915</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>-8.891328783900011e-16</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>-1.942892454509541e-07</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>1.530921263289087e-16</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>-0.0001659335177280807</v>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>-2.265442909249824e-16</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>-2.219799742742411e-15</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>-1.263136022281428e-06</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>1.525494836327788e-16</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>-5.794413735969998e-16</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>-1.942892454509541e-07</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-8.891328783900011e-16</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>0.0004978005531828473</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>-2.265442909249824e-16</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>-0.0001659335177280807</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>-1.530921263289087e-16</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>-1.263136022281428e-06</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AC8" t="n">
         <v>-2.219799742742411e-15</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AD8" t="n">
         <v>0.004231960428275111</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AE8" t="n">
         <v>-5.794413735969998e-16</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AF8" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AG8" t="n">
         <v>-1.525494836327788e-16</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AH8" t="n">
         <v>0.168877790739215</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AI8" t="n">
         <v>1.020563685019457e-13</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="n">
         <v>3.534950110406498e-13</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AK8" t="n">
         <v>1.004399389143434e-15</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AL8" t="n">
         <v>0.6755111629511581</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AM8" t="n">
         <v>3.057675499107009e-13</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AN8" t="n">
         <v>-0.168877790739215</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AO8" t="n">
         <v>-1.020563685019457e-13</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AP8" t="n">
         <v>-3.534950110406498e-13</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AQ8" t="n">
         <v>-1.004399389143434e-15</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AR8" t="n">
         <v>-0.6755111629532804</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AS8" t="n">
         <v>3.065706611009732e-13</v>
       </c>
     </row>
@@ -3645,127 +4949,138 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>12</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>-1.068846776830301e-06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.781411294717168e-07</v>
+      </c>
+      <c r="H9" t="n">
         <v>-0.1688777907391875</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>-35.62822589434336</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>-0.0004978005531846971</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>-8.891328499999085e-16</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>-1.94289245450664e-07</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>1.530956406052565e-16</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>-0.0001659335177284097</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>-2.264856906194544e-16</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>-2.219801240530538e-15</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>-1.263136022280965e-06</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>1.525337304621532e-16</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>-5.789503694433393e-16</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>-1.94289245450664e-07</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>-8.891328499999085e-16</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>0.0004978005531846971</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>-2.264856906194544e-16</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>-0.0001659335177284097</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>-1.530956406052565e-16</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>-1.263136022280965e-06</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AC9" t="n">
         <v>-2.219801240530538e-15</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
         <v>0.00423196042827995</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
         <v>-5.789503694433393e-16</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AF9" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AG9" t="n">
         <v>-1.525337304621532e-16</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
         <v>0.1688777907391875</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
         <v>1.020658017410055e-13</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AJ9" t="n">
         <v>1.294520046712933e-13</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AK9" t="n">
         <v>1.00316870126798e-15</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AL9" t="n">
         <v>0.6755111629518573</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AM9" t="n">
         <v>3.057815917171203e-13</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AN9" t="n">
         <v>-0.1688777907391875</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AO9" t="n">
         <v>-1.020658017410055e-13</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AP9" t="n">
         <v>-1.294520046712933e-13</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AQ9" t="n">
         <v>-1.00316870126798e-15</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AR9" t="n">
         <v>-0.6755111629526342</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AS9" t="n">
         <v>3.06613218728913e-13</v>
       </c>
     </row>
@@ -3773,127 +5088,138 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>13</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>1.683885617314446e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.806476028857409e-08</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.02660539275356824</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>5.612952057714819</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>2.207429876228768e-15</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>-0.009998736863977724</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>-1.513191775452895e-16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="N10" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>-5.793042247975463e-16</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>3.28462098894533e-15</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>-0.009998568475415992</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>-9.957666828069171e-17</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>-0.001222599374437406</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>-8.802264234440092e-16</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>-0.009998736863977724</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>2.207429876228768e-15</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>0.00423196042827995</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
         <v>-5.793042247975463e-16</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>1.513191775452895e-16</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>-0.009998568475415992</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
         <v>3.28462098894533e-15</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AD10" t="n">
         <v>0.01113611787350202</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AE10" t="n">
         <v>-8.802264234440092e-16</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AF10" t="n">
         <v>-0.001222599374437406</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AG10" t="n">
         <v>9.957666828069171e-17</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AH10" t="n">
         <v>-0.02660539275348128</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AI10" t="n">
         <v>-8.004421522552583e-14</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AJ10" t="n">
         <v>1.729727472365994e-13</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AK10" t="n">
         <v>8.564708730707019e-16</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AL10" t="n">
         <v>0.1064215710118925</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AM10" t="n">
         <v>-2.018431888207753e-13</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AN10" t="n">
         <v>0.02660539275348128</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AO10" t="n">
         <v>8.004421522552583e-14</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AP10" t="n">
         <v>-1.729727472365994e-13</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AQ10" t="n">
         <v>-8.564708730707019e-16</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AR10" t="n">
         <v>-0.1064215710129304</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AS10" t="n">
         <v>-2.784221025323803e-13</v>
       </c>
     </row>
@@ -3901,127 +5227,138 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>14</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>6</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
+        <v>1.68388561734914e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.806476028915234e-08</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.02660539275411641</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>5.612952057830467</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>2.20743100433644e-15</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>-0.009998736863977717</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>-1.511978472574226e-16</v>
       </c>
-      <c r="K11" t="n">
+      <c r="N11" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>-5.791783144273565e-16</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
         <v>-0.01113611787349452</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>3.284615749884662e-15</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>-0.009998568475415982</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>-9.957497490218503e-17</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>-8.795874158562031e-16</v>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>-0.009998736863977717</v>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>2.20743100433644e-15</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>0.004231960428275111</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
         <v>-5.791783144273565e-16</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>1.511978472574226e-16</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>-0.009998568475415982</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>3.284615749884662e-15</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
         <v>0.01113611787349452</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
         <v>-8.795874158562031e-16</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AG11" t="n">
         <v>9.957497490218503e-17</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AH11" t="n">
         <v>-0.0266053927541634</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AI11" t="n">
         <v>-8.013368217045158e-14</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AJ11" t="n">
         <v>3.987921104453562e-13</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AK11" t="n">
         <v>8.550105194513328e-16</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AL11" t="n">
         <v>0.1064215710113263</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AM11" t="n">
         <v>-2.022001209684786e-13</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AN11" t="n">
         <v>0.0266053927541634</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AO11" t="n">
         <v>8.013368217045158e-14</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AP11" t="n">
         <v>-3.987921104453562e-13</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AQ11" t="n">
         <v>-8.550105194513328e-16</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AR11" t="n">
         <v>-0.1064215710137209</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AS11" t="n">
         <v>-2.786019720542305e-13</v>
       </c>
     </row>
@@ -4029,127 +5366,138 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>15</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
+        <v>-1.683885617332492e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.806476028887486e-08</v>
+      </c>
+      <c r="H12" t="n">
         <v>-0.02660539275385337</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>-5.612952057774971</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>-2.219799742742411e-15</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>-1.263136022281428e-06</v>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>1.525494836327788e-16</v>
       </c>
-      <c r="K12" t="n">
+      <c r="N12" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="L12" t="n">
+      <c r="O12" t="n">
         <v>-5.794413735969998e-16</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
         <v>-0.01113611787349453</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>-3.304815612337873e-15</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>-1.431524584014678e-06</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>1.007394783138497e-16</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>-8.801109181113563e-16</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>-1.263136022281428e-06</v>
       </c>
-      <c r="T12" t="n">
+      <c r="W12" t="n">
         <v>-2.219799742742411e-15</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>0.004231960428275111</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
         <v>-5.794413735969998e-16</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>-1.525494836327788e-16</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>-1.431524584014678e-06</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
         <v>-3.304815612337873e-15</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AD12" t="n">
         <v>0.01113611787349453</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AE12" t="n">
         <v>-8.801109181113563e-16</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AF12" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
         <v>-1.007394783138497e-16</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AH12" t="n">
         <v>0.02660539275385337</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AI12" t="n">
         <v>8.020341599304231e-14</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AJ12" t="n">
         <v>3.983480212355062e-13</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AK12" t="n">
         <v>8.557517805408608e-16</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AL12" t="n">
         <v>0.1064215710113285</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AM12" t="n">
         <v>2.022708440431196e-13</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AN12" t="n">
         <v>-0.02660539275385337</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AO12" t="n">
         <v>-8.020341599304231e-14</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AP12" t="n">
         <v>-3.983480212355062e-13</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AQ12" t="n">
         <v>-8.557517805408608e-16</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AR12" t="n">
         <v>-0.1064215710137182</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AS12" t="n">
         <v>2.789496519151347e-13</v>
       </c>
     </row>
@@ -4157,127 +5505,138 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>16</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>6</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>-1.683885617333849e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-2.806476028889748e-08</v>
+      </c>
+      <c r="H13" t="n">
         <v>-0.02660539275387482</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>-5.612952057779497</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>-2.219801240530538e-15</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>-1.263136022280965e-06</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>1.525337304621532e-16</v>
       </c>
-      <c r="K13" t="n">
+      <c r="N13" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
         <v>-5.789503694433393e-16</v>
       </c>
-      <c r="M13" t="n">
+      <c r="P13" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>-3.304817884023839e-15</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>-1.43152458401435e-06</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>1.007901242459449e-16</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>-0.001222599374437407</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>-8.800237745202832e-16</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>-1.263136022280965e-06</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>-2.219801240530538e-15</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>0.00423196042827995</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>-5.789503694433393e-16</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>-1.525337304621532e-16</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>-1.43152458401435e-06</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>-3.304817884023839e-15</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AD13" t="n">
         <v>0.01113611787350202</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AE13" t="n">
         <v>-8.800237745202832e-16</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AF13" t="n">
         <v>-0.001222599374437407</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AG13" t="n">
         <v>-1.007901242459449e-16</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AH13" t="n">
         <v>0.02660539275387483</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AI13" t="n">
         <v>8.017778624435488e-14</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AJ13" t="n">
         <v>1.73749903353837e-13</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AK13" t="n">
         <v>8.569012298343786e-16</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AL13" t="n">
         <v>0.106421571011891</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AM13" t="n">
         <v>2.022430901330703e-13</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AN13" t="n">
         <v>-0.02660539275387483</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AO13" t="n">
         <v>-8.017778624435488e-14</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AP13" t="n">
         <v>-1.73749903353837e-13</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AQ13" t="n">
         <v>-8.569012298343786e-16</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AR13" t="n">
         <v>-0.1064215710129344</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AS13" t="n">
         <v>2.788236273330586e-13</v>
       </c>
     </row>
@@ -4285,127 +5644,138 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>17</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>2.59006837140946e-08</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.316780619015766e-09</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.004092308026826946</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>0.8633561238031532</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>3.28462098894533e-15</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>-0.009998568475415992</v>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>-9.957666828069171e-17</v>
       </c>
-      <c r="K14" t="n">
+      <c r="N14" t="n">
         <v>-0.001222599374437406</v>
       </c>
-      <c r="L14" t="n">
+      <c r="O14" t="n">
         <v>-8.802264234440092e-16</v>
       </c>
-      <c r="M14" t="n">
+      <c r="P14" t="n">
         <v>-0.01853807587190909</v>
       </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
         <v>3.845064052013146e-15</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>-0.009998542574732278</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>-4.180501003454598e-17</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>-1.003618666593276e-15</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>-0.009998568475415992</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>3.28462098894533e-15</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>0.01113611787350202</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>-8.802264234440092e-16</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Z14" t="n">
         <v>-0.001222599374437406</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AA14" t="n">
         <v>9.957666828069171e-17</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>-0.009998542574732278</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AC14" t="n">
         <v>3.845064052013146e-15</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AD14" t="n">
         <v>0.01853807587190909</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AE14" t="n">
         <v>-1.003618666593276e-15</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AF14" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AG14" t="n">
         <v>4.180501003454598e-17</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AH14" t="n">
         <v>-0.004092308026883984</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AI14" t="n">
         <v>-3.362018027011895e-14</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AJ14" t="n">
         <v>3.466116282879739e-13</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AK14" t="n">
         <v>3.51193307424836e-16</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AL14" t="n">
         <v>0.01636923210568808</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AM14" t="n">
         <v>-5.810951370820892e-14</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AN14" t="n">
         <v>0.004092308026883984</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AO14" t="n">
         <v>3.362018027011895e-14</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AP14" t="n">
         <v>-3.466116282879739e-13</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AQ14" t="n">
         <v>-3.51193307424836e-16</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AR14" t="n">
         <v>-0.01636923210776953</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AS14" t="n">
         <v>-1.436115679125046e-13</v>
       </c>
     </row>
@@ -4413,127 +5783,138 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>18</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
+        <v>2.59006837140946e-08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.316780619015766e-09</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.004092308026826946</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>0.8633561238031532</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>-0.01113611787349452</v>
       </c>
-      <c r="H15" t="n">
+      <c r="K15" t="n">
         <v>3.284615749884662e-15</v>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
         <v>-0.009998568475415982</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>-9.957497490218503e-17</v>
       </c>
-      <c r="K15" t="n">
+      <c r="N15" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="L15" t="n">
+      <c r="O15" t="n">
         <v>-8.795874158562031e-16</v>
       </c>
-      <c r="M15" t="n">
+      <c r="P15" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
         <v>3.845065573465923e-15</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
         <v>-0.009998542574732268</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
         <v>-4.187830652248113e-17</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>-0.001244719958365369</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>-1.005467541231768e-15</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>-0.009998568475415982</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>3.284615749884662e-15</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>0.01113611787349452</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>-8.795874158562031e-16</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AA15" t="n">
         <v>9.957497490218503e-17</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
         <v>-0.009998542574732268</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AC15" t="n">
         <v>3.845065573465923e-15</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AD15" t="n">
         <v>0.01853807587190073</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AE15" t="n">
         <v>-1.005467541231768e-15</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AF15" t="n">
         <v>-0.001244719958365369</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
         <v>4.187830652248113e-17</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AH15" t="n">
         <v>-0.004092308026883984</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AI15" t="n">
         <v>-3.35688615624581e-14</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AJ15" t="n">
         <v>3.634870182622763e-13</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AK15" t="n">
         <v>3.582742029919923e-16</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AL15" t="n">
         <v>0.01636923210576091</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AM15" t="n">
         <v>-5.801105008639339e-14</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AN15" t="n">
         <v>0.004092308026883984</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AO15" t="n">
         <v>3.35688615624581e-14</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AP15" t="n">
         <v>-3.634870182622763e-13</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AQ15" t="n">
         <v>-3.582742029919923e-16</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AR15" t="n">
         <v>-0.01636923210794006</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AS15" t="n">
         <v>-1.434021192883554e-13</v>
       </c>
     </row>
@@ -4541,127 +5922,138 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>19</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
+        <v>-2.590068371486095e-08</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-4.316780619143492e-09</v>
+      </c>
+      <c r="H16" t="n">
         <v>-0.00409230802694803</v>
       </c>
-      <c r="F16" t="n">
+      <c r="I16" t="n">
         <v>-0.8633561238286983</v>
       </c>
-      <c r="G16" t="n">
+      <c r="J16" t="n">
         <v>-0.01113611787349453</v>
       </c>
-      <c r="H16" t="n">
+      <c r="K16" t="n">
         <v>-3.304815612337873e-15</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>-1.431524584014678e-06</v>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>1.007394783138497e-16</v>
       </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>-8.801109181113563e-16</v>
       </c>
-      <c r="M16" t="n">
+      <c r="P16" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="N16" t="n">
+      <c r="Q16" t="n">
         <v>-3.870980034180524e-15</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>-1.457425267729539e-06</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>4.302749958412686e-17</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>-0.001244719958365368</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>-1.004357076261401e-15</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>-1.431524584014678e-06</v>
       </c>
-      <c r="T16" t="n">
+      <c r="W16" t="n">
         <v>-3.304815612337873e-15</v>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
         <v>0.01113611787349453</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
         <v>-8.801109181113563e-16</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
         <v>-1.007394783138497e-16</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>-1.457425267729539e-06</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AC16" t="n">
         <v>-3.870980034180524e-15</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AD16" t="n">
         <v>0.01853807587190073</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AE16" t="n">
         <v>-1.004357076261401e-15</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AF16" t="n">
         <v>-0.001244719958365368</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AG16" t="n">
         <v>-4.302749958412686e-17</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AH16" t="n">
         <v>0.004092308026948044</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AI16" t="n">
         <v>3.32663270766845e-14</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AJ16" t="n">
         <v>3.629319067499637e-13</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AK16" t="n">
         <v>3.536236808885884e-16</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AL16" t="n">
         <v>0.01636923210576025</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AM16" t="n">
         <v>5.70921169700583e-14</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AN16" t="n">
         <v>-0.004092308026948044</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AO16" t="n">
         <v>-3.32663270766845e-14</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AP16" t="n">
         <v>-3.629319067499637e-13</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AQ16" t="n">
         <v>-3.536236808885884e-16</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AR16" t="n">
         <v>-0.01636923210793961</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AS16" t="n">
         <v>1.425058454900481e-13</v>
       </c>
     </row>
@@ -4669,127 +6061,138 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>20</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
+        <v>-2.590068371506487e-08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-4.316780619177479e-09</v>
+      </c>
+      <c r="H17" t="n">
         <v>-0.00409230802698025</v>
       </c>
-      <c r="F17" t="n">
+      <c r="I17" t="n">
         <v>-0.8633561238354956</v>
       </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="H17" t="n">
+      <c r="K17" t="n">
         <v>-3.304817884023839e-15</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>-1.43152458401435e-06</v>
       </c>
-      <c r="J17" t="n">
+      <c r="M17" t="n">
         <v>1.007901242459449e-16</v>
       </c>
-      <c r="K17" t="n">
+      <c r="N17" t="n">
         <v>-0.001222599374437407</v>
       </c>
-      <c r="L17" t="n">
+      <c r="O17" t="n">
         <v>-8.800237745202832e-16</v>
       </c>
-      <c r="M17" t="n">
+      <c r="P17" t="n">
         <v>-0.01853807587190909</v>
       </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
         <v>-3.870974767127275e-15</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>-1.457425267729414e-06</v>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>4.277158646686195e-17</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="T17" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>-1.004678364397376e-15</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>-1.43152458401435e-06</v>
       </c>
-      <c r="T17" t="n">
+      <c r="W17" t="n">
         <v>-3.304817884023839e-15</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>0.01113611787350202</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>-8.800237745202832e-16</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
         <v>-0.001222599374437407</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>-1.007901242459449e-16</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>-1.457425267729414e-06</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
         <v>-3.870974767127275e-15</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
         <v>0.01853807587190909</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AE17" t="n">
         <v>-1.004678364397376e-15</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AF17" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AG17" t="n">
         <v>-4.277158646686195e-17</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AH17" t="n">
         <v>0.00409230802698024</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AI17" t="n">
         <v>3.341636523803729e-14</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AJ17" t="n">
         <v>3.465006059855114e-13</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AK17" t="n">
         <v>3.547861404194171e-16</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AL17" t="n">
         <v>0.01636923210568919</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AM17" t="n">
         <v>5.73153777575905e-14</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AN17" t="n">
         <v>-0.00409230802698024</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AO17" t="n">
         <v>-3.341636523803729e-14</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AP17" t="n">
         <v>-3.465006059855114e-13</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AQ17" t="n">
         <v>-3.547861404194171e-16</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AR17" t="n">
         <v>-0.01636923210776908</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AS17" t="n">
         <v>1.431828136706332e-13</v>
       </c>
     </row>
@@ -4797,127 +6200,138 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>6</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>8</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
+        <v>4.245243044716826e-22</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.306553805896032e-23</v>
+      </c>
+      <c r="H18" t="n">
         <v>5.030613007989438e-17</v>
       </c>
-      <c r="F18" t="n">
+      <c r="I18" t="n">
         <v>1.061310761179206e-14</v>
       </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
         <v>-0.000497800553184697</v>
       </c>
-      <c r="H18" t="n">
+      <c r="K18" t="n">
         <v>8.848921481134703e-16</v>
       </c>
-      <c r="I18" t="n">
+      <c r="L18" t="n">
         <v>1.942892454476922e-07</v>
       </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
         <v>-1.521497120175572e-16</v>
       </c>
-      <c r="K18" t="n">
+      <c r="N18" t="n">
         <v>-0.0001659335177284096</v>
       </c>
-      <c r="L18" t="n">
+      <c r="O18" t="n">
         <v>-2.265660456427604e-16</v>
       </c>
-      <c r="M18" t="n">
+      <c r="P18" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="N18" t="n">
+      <c r="Q18" t="n">
         <v>8.848925726377748e-16</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
         <v>1.942892454508281e-07</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
         <v>-1.522206922017046e-16</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
         <v>-0.0001659335177280808</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>-2.265401975707692e-16</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>8.848921481134703e-16</v>
       </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
         <v>0.000497800553184697</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>1.942892454476922e-07</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
         <v>-0.0001659335177284096</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
         <v>1.521497120175572e-16</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AA18" t="n">
         <v>-2.265660456427604e-16</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>8.848925726377748e-16</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AC18" t="n">
         <v>0.0004978005531828473</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AD18" t="n">
         <v>1.942892454508281e-07</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AE18" t="n">
         <v>-0.0001659335177280808</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AF18" t="n">
         <v>1.522206922017046e-16</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AG18" t="n">
         <v>-2.265401975707692e-16</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AH18" t="n">
         <v>-5.030613008684149e-17</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AI18" t="n">
         <v>3.885780586188048e-15</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AJ18" t="n">
         <v>-1.270205090833757e-13</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AK18" t="n">
         <v>-7.01804066249867e-16</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AL18" t="n">
         <v>5.0804263836559e-13</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AM18" t="n">
         <v>1.551536676913656e-14</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AN18" t="n">
         <v>5.030613008684149e-17</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AO18" t="n">
         <v>-3.885780586188048e-15</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AP18" t="n">
         <v>1.270205090833757e-13</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AQ18" t="n">
         <v>7.01804066249867e-16</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AR18" t="n">
         <v>5.081214343014151e-13</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AS18" t="n">
         <v>1.554312234475219e-14</v>
       </c>
     </row>
@@ -4925,127 +6339,138 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>7</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>8</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="H19" t="n">
+      <c r="K19" t="n">
         <v>8.848925726377748e-16</v>
       </c>
-      <c r="I19" t="n">
+      <c r="L19" t="n">
         <v>1.942892454508281e-07</v>
       </c>
-      <c r="J19" t="n">
+      <c r="M19" t="n">
         <v>-1.522206922017046e-16</v>
       </c>
-      <c r="K19" t="n">
+      <c r="N19" t="n">
         <v>-0.0001659335177280808</v>
       </c>
-      <c r="L19" t="n">
+      <c r="O19" t="n">
         <v>-2.265401975707692e-16</v>
       </c>
-      <c r="M19" t="n">
+      <c r="P19" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
         <v>-8.891328783900011e-16</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
         <v>-1.942892454509541e-07</v>
       </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
         <v>1.530921263289087e-16</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="T19" t="n">
         <v>-0.0001659335177280807</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>-2.265442909249824e-16</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>8.848925726377748e-16</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>1.942892454508281e-07</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>-1.522206922017046e-16</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>-0.0001659335177280808</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AA19" t="n">
         <v>-2.265401975707692e-16</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AC19" t="n">
         <v>-8.891328783900011e-16</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AD19" t="n">
         <v>-1.942892454509541e-07</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AE19" t="n">
         <v>1.530921263289087e-16</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AF19" t="n">
         <v>-0.0001659335177280807</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AG19" t="n">
         <v>-2.265442909249824e-16</v>
       </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>-3.986894838778718e-15</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AJ19" t="n">
         <v>0.1381800899578367</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AK19" t="n">
         <v>-6.517254395557321e-16</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AL19" t="n">
         <v>-0.5527203598313468</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AM19" t="n">
         <v>-1.594530754352647e-14</v>
       </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
         <v>3.986894838778718e-15</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AP19" t="n">
         <v>-0.1381800899578367</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AQ19" t="n">
         <v>6.517254395557321e-16</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AR19" t="n">
         <v>-0.5527203598313467</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AS19" t="n">
         <v>-1.594985116670313e-14</v>
       </c>
     </row>
@@ -5053,127 +6478,138 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>7</v>
-      </c>
-      <c r="C20" t="n">
-        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-2.839009265922372e-23</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-3.548761582402965e-24</v>
+      </c>
+      <c r="H20" t="n">
         <v>-3.364225980118011e-18</v>
       </c>
-      <c r="F20" t="n">
+      <c r="I20" t="n">
         <v>-7.09752316480593e-16</v>
       </c>
-      <c r="G20" t="n">
+      <c r="J20" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="H20" t="n">
+      <c r="K20" t="n">
         <v>-8.891328783900011e-16</v>
       </c>
-      <c r="I20" t="n">
+      <c r="L20" t="n">
         <v>-1.942892454509541e-07</v>
       </c>
-      <c r="J20" t="n">
+      <c r="M20" t="n">
         <v>1.530921263289087e-16</v>
       </c>
-      <c r="K20" t="n">
+      <c r="N20" t="n">
         <v>-0.0001659335177280807</v>
       </c>
-      <c r="L20" t="n">
+      <c r="O20" t="n">
         <v>-2.265442909249824e-16</v>
       </c>
-      <c r="M20" t="n">
+      <c r="P20" t="n">
         <v>-0.0004978005531846971</v>
       </c>
-      <c r="N20" t="n">
+      <c r="Q20" t="n">
         <v>-8.891328499999085e-16</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
         <v>-1.94289245450664e-07</v>
       </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
         <v>1.530956406052565e-16</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="T20" t="n">
         <v>-0.0001659335177284097</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>-2.264856906194544e-16</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>8.891328783900011e-16</v>
       </c>
-      <c r="T20" t="n">
+      <c r="W20" t="n">
         <v>-0.0004978005531828473</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>-1.942892454509541e-07</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>0.0001659335177280807</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
         <v>1.530921263289087e-16</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AA20" t="n">
         <v>-2.265442909249824e-16</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>8.891328499999085e-16</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AC20" t="n">
         <v>-0.0004978005531846971</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AD20" t="n">
         <v>-1.94289245450664e-07</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AE20" t="n">
         <v>0.0001659335177284097</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AF20" t="n">
         <v>1.530956406052565e-16</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AG20" t="n">
         <v>-2.264856906194544e-16</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AH20" t="n">
         <v>3.364225984971083e-18</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AI20" t="n">
         <v>3.934352843515398e-15</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AJ20" t="n">
         <v>-1.274808412077357e-13</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AK20" t="n">
         <v>-7.022919572274855e-16</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AL20" t="n">
         <v>5.099214167321203e-13</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AM20" t="n">
         <v>1.568190022283034e-14</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AN20" t="n">
         <v>-3.364225984971083e-18</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AO20" t="n">
         <v>-3.934352843515398e-15</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AP20" t="n">
         <v>1.274808412077357e-13</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AQ20" t="n">
         <v>7.022919572274855e-16</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AR20" t="n">
         <v>5.099253264822925e-13</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AS20" t="n">
         <v>1.576516694967722e-14</v>
       </c>
     </row>
@@ -5181,127 +6617,138 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>8</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
+        <v>-1.084202172485504e-19</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.355252715606881e-20</v>
+      </c>
+      <c r="H21" t="n">
         <v>-1.284779574395323e-14</v>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>-2.710505431213761e-12</v>
       </c>
-      <c r="G21" t="n">
+      <c r="J21" t="n">
         <v>-0.0004978005531846971</v>
       </c>
-      <c r="H21" t="n">
+      <c r="K21" t="n">
         <v>-8.891328499999085e-16</v>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>-1.94289245450664e-07</v>
       </c>
-      <c r="J21" t="n">
+      <c r="M21" t="n">
         <v>1.530956406052565e-16</v>
       </c>
-      <c r="K21" t="n">
+      <c r="N21" t="n">
         <v>-0.0001659335177284097</v>
       </c>
-      <c r="L21" t="n">
+      <c r="O21" t="n">
         <v>-2.264856906194544e-16</v>
       </c>
-      <c r="M21" t="n">
+      <c r="P21" t="n">
         <v>-0.000497800553184697</v>
       </c>
-      <c r="N21" t="n">
+      <c r="Q21" t="n">
         <v>8.848921481134703e-16</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
         <v>1.942892454476922e-07</v>
       </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
         <v>-1.521497120175572e-16</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>-0.0001659335177284096</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>-2.265660456427604e-16</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>0.0004978005531846971</v>
       </c>
-      <c r="T21" t="n">
+      <c r="W21" t="n">
         <v>-8.891328499999085e-16</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>1.94289245450664e-07</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>-1.530956406052565e-16</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
         <v>-0.0001659335177284097</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AA21" t="n">
         <v>2.264856906194544e-16</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
         <v>0.000497800553184697</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AC21" t="n">
         <v>8.848921481134703e-16</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AD21" t="n">
         <v>-1.942892454476922e-07</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AE21" t="n">
         <v>1.521497120175572e-16</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AF21" t="n">
         <v>-0.0001659335177284096</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AG21" t="n">
         <v>2.265660456427604e-16</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AH21" t="n">
         <v>1.4210854715202e-14</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AI21" t="n">
         <v>3.973308852973428e-15</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AJ21" t="n">
         <v>0.1381800899581102</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AK21" t="n">
         <v>-6.515814257910062e-16</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AL21" t="n">
         <v>-0.5527203598324407</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AM21" t="n">
         <v>1.584863837395873e-14</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AN21" t="n">
         <v>-1.4210854715202e-14</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AO21" t="n">
         <v>-3.973308852973428e-15</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AP21" t="n">
         <v>-0.1381800899581102</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AQ21" t="n">
         <v>6.515814257910062e-16</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AR21" t="n">
         <v>-0.5527203598324405</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AS21" t="n">
         <v>1.593783244982845e-14</v>
       </c>
     </row>
@@ -5309,127 +6756,138 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>8</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
+        <v>1.128107672762931e-21</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.410134590953663e-22</v>
+      </c>
+      <c r="H22" t="n">
         <v>1.336807592224073e-16</v>
       </c>
-      <c r="F22" t="n">
+      <c r="I22" t="n">
         <v>2.820269181907326e-14</v>
       </c>
-      <c r="G22" t="n">
+      <c r="J22" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="H22" t="n">
+      <c r="K22" t="n">
         <v>2.207429876228768e-15</v>
       </c>
-      <c r="I22" t="n">
+      <c r="L22" t="n">
         <v>-0.009998736863977724</v>
       </c>
-      <c r="J22" t="n">
+      <c r="M22" t="n">
         <v>-1.513191775452895e-16</v>
       </c>
-      <c r="K22" t="n">
+      <c r="N22" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="L22" t="n">
+      <c r="O22" t="n">
         <v>-5.793042247975463e-16</v>
       </c>
-      <c r="M22" t="n">
+      <c r="P22" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="N22" t="n">
+      <c r="Q22" t="n">
         <v>2.20743100433644e-15</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
         <v>-0.009998736863977717</v>
       </c>
-      <c r="P22" t="n">
+      <c r="S22" t="n">
         <v>-1.511978472574226e-16</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="T22" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>-5.791783144273565e-16</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>2.207429876228768e-15</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>0.00423196042827995</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>-0.009998736863977724</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
         <v>1.513191775452895e-16</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AA22" t="n">
         <v>-5.793042247975463e-16</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>2.20743100433644e-15</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AC22" t="n">
         <v>0.004231960428275111</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AD22" t="n">
         <v>-0.009998736863977717</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AE22" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AF22" t="n">
         <v>1.511978472574226e-16</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AG22" t="n">
         <v>-5.791783144273565e-16</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AH22" t="n">
         <v>-1.336807591937417e-16</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AI22" t="n">
         <v>2.142730437526552e-14</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AJ22" t="n">
         <v>-1.266629055343862e-13</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AK22" t="n">
         <v>-7.80191883320569e-16</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AL22" t="n">
         <v>5.062255883614868e-13</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AM22" t="n">
         <v>8.570921750106208e-14</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AN22" t="n">
         <v>1.336807591937417e-16</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AO22" t="n">
         <v>-2.142730437526552e-14</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AP22" t="n">
         <v>1.266629055343862e-13</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AQ22" t="n">
         <v>7.80191883320569e-16</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AR22" t="n">
         <v>5.061894774939023e-13</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AS22" t="n">
         <v>8.570921750106208e-14</v>
       </c>
     </row>
@@ -5437,127 +6895,138 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>10</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>11</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>8</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="H23" t="n">
+      <c r="K23" t="n">
         <v>2.20743100433644e-15</v>
       </c>
-      <c r="I23" t="n">
+      <c r="L23" t="n">
         <v>-0.009998736863977717</v>
       </c>
-      <c r="J23" t="n">
+      <c r="M23" t="n">
         <v>-1.511978472574226e-16</v>
       </c>
-      <c r="K23" t="n">
+      <c r="N23" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="L23" t="n">
+      <c r="O23" t="n">
         <v>-5.791783144273565e-16</v>
       </c>
-      <c r="M23" t="n">
+      <c r="P23" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="N23" t="n">
+      <c r="Q23" t="n">
         <v>-2.219799742742411e-15</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
         <v>-1.263136022281428e-06</v>
       </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
         <v>1.525494836327788e-16</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="T23" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>-5.794413735969998e-16</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="T23" t="n">
+      <c r="W23" t="n">
         <v>2.20743100433644e-15</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>-0.009998736863977717</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>-1.511978472574226e-16</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AA23" t="n">
         <v>-5.791783144273565e-16</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
         <v>-2.219799742742411e-15</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AD23" t="n">
         <v>-1.263136022281428e-06</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AE23" t="n">
         <v>1.525494836327788e-16</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AF23" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AG23" t="n">
         <v>-5.794413735969998e-16</v>
       </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
         <v>-2.156674552224533e-14</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AJ23" t="n">
         <v>-0.1422723979854889</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AK23" t="n">
         <v>-6.483837255540837e-16</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AL23" t="n">
         <v>0.5690895919419561</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AM23" t="n">
         <v>-8.612098424982906e-14</v>
       </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
         <v>2.156674552224533e-14</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AP23" t="n">
         <v>0.1422723979854889</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AQ23" t="n">
         <v>6.483837255540837e-16</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AR23" t="n">
         <v>0.5690895919419559</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AS23" t="n">
         <v>-8.641297992813301e-14</v>
       </c>
     </row>
@@ -5565,127 +7034,138 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>11</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>12</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
+        <v>1.497788127626146e-21</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.872235159532683e-22</v>
+      </c>
+      <c r="H24" t="n">
         <v>1.774878931236983e-16</v>
       </c>
-      <c r="F24" t="n">
+      <c r="I24" t="n">
         <v>3.744470319065365e-14</v>
       </c>
-      <c r="G24" t="n">
+      <c r="J24" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="H24" t="n">
+      <c r="K24" t="n">
         <v>-2.219799742742411e-15</v>
       </c>
-      <c r="I24" t="n">
+      <c r="L24" t="n">
         <v>-1.263136022281428e-06</v>
       </c>
-      <c r="J24" t="n">
+      <c r="M24" t="n">
         <v>1.525494836327788e-16</v>
       </c>
-      <c r="K24" t="n">
+      <c r="N24" t="n">
         <v>-0.001078786440636485</v>
       </c>
-      <c r="L24" t="n">
+      <c r="O24" t="n">
         <v>-5.794413735969998e-16</v>
       </c>
-      <c r="M24" t="n">
+      <c r="P24" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
         <v>-2.219801240530538e-15</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
         <v>-1.263136022280965e-06</v>
       </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
         <v>1.525337304621532e-16</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="T24" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
         <v>-5.789503694433393e-16</v>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>2.219799742742411e-15</v>
       </c>
-      <c r="T24" t="n">
+      <c r="W24" t="n">
         <v>-0.004231960428275111</v>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
         <v>-1.263136022281428e-06</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
         <v>0.001078786440636485</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Z24" t="n">
         <v>1.525494836327788e-16</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
         <v>-5.794413735969998e-16</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>2.219801240530538e-15</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AC24" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AD24" t="n">
         <v>-1.263136022280965e-06</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AE24" t="n">
         <v>0.00107878644063685</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AF24" t="n">
         <v>1.525337304621532e-16</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AG24" t="n">
         <v>-5.789503694433393e-16</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AH24" t="n">
         <v>-1.774878931412836e-16</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AI24" t="n">
         <v>2.148281552649678e-14</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AJ24" t="n">
         <v>-1.270391248829942e-13</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AK24" t="n">
         <v>-7.784571598445922e-16</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AL24" t="n">
         <v>5.081653015142231e-13</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AM24" t="n">
         <v>8.570921750106208e-14</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AN24" t="n">
         <v>1.774878931412836e-16</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AO24" t="n">
         <v>-2.148281552649678e-14</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AP24" t="n">
         <v>1.270391248829942e-13</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AQ24" t="n">
         <v>7.784571598445922e-16</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AR24" t="n">
         <v>5.081478059699478e-13</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AS24" t="n">
         <v>8.615330671091215e-14</v>
       </c>
     </row>
@@ -5693,127 +7173,138 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>12</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>9</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>8</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="H25" t="n">
+      <c r="K25" t="n">
         <v>-2.219801240530538e-15</v>
       </c>
-      <c r="I25" t="n">
+      <c r="L25" t="n">
         <v>-1.263136022280965e-06</v>
       </c>
-      <c r="J25" t="n">
+      <c r="M25" t="n">
         <v>1.525337304621532e-16</v>
       </c>
-      <c r="K25" t="n">
+      <c r="N25" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="L25" t="n">
+      <c r="O25" t="n">
         <v>-5.789503694433393e-16</v>
       </c>
-      <c r="M25" t="n">
+      <c r="P25" t="n">
         <v>-0.00423196042827995</v>
       </c>
-      <c r="N25" t="n">
+      <c r="Q25" t="n">
         <v>2.207429876228768e-15</v>
       </c>
-      <c r="O25" t="n">
+      <c r="R25" t="n">
         <v>-0.009998736863977724</v>
       </c>
-      <c r="P25" t="n">
+      <c r="S25" t="n">
         <v>-1.513191775452895e-16</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="T25" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>-5.793042247975463e-16</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>0.00423196042827995</v>
       </c>
-      <c r="T25" t="n">
+      <c r="W25" t="n">
         <v>-2.219801240530538e-15</v>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>1.263136022280965e-06</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>-1.525337304621532e-16</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
         <v>5.789503694433393e-16</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>0.00423196042827995</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AC25" t="n">
         <v>2.207429876228768e-15</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AD25" t="n">
         <v>0.009998736863977724</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AE25" t="n">
         <v>1.513191775452895e-16</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AF25" t="n">
         <v>-0.00107878644063685</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AG25" t="n">
         <v>5.793042247975463e-16</v>
       </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
         <v>2.141473676500339e-14</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AJ25" t="n">
         <v>-0.1422723979851855</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AK25" t="n">
         <v>-6.486090920928102e-16</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AL25" t="n">
         <v>0.5690895919407426</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AM25" t="n">
         <v>8.54625573384283e-14</v>
       </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
         <v>-2.141473676500339e-14</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AP25" t="n">
         <v>0.1422723979851855</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AQ25" t="n">
         <v>6.486090920928102e-16</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AR25" t="n">
         <v>0.5690895919407422</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AS25" t="n">
         <v>8.585533678159801e-14</v>
       </c>
     </row>
@@ -5821,127 +7312,138 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>13</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>14</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>8</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
+        <v>-5.239060668061288e-21</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-6.54882583507661e-22</v>
+      </c>
+      <c r="H26" t="n">
         <v>-6.208286891652626e-16</v>
       </c>
-      <c r="F26" t="n">
+      <c r="I26" t="n">
         <v>-1.309765167015322e-13</v>
       </c>
-      <c r="G26" t="n">
+      <c r="J26" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="H26" t="n">
+      <c r="K26" t="n">
         <v>3.28462098894533e-15</v>
       </c>
-      <c r="I26" t="n">
+      <c r="L26" t="n">
         <v>-0.009998568475415992</v>
       </c>
-      <c r="J26" t="n">
+      <c r="M26" t="n">
         <v>-9.957666828069171e-17</v>
       </c>
-      <c r="K26" t="n">
+      <c r="N26" t="n">
         <v>-0.001222599374437406</v>
       </c>
-      <c r="L26" t="n">
+      <c r="O26" t="n">
         <v>-8.802264234440092e-16</v>
       </c>
-      <c r="M26" t="n">
+      <c r="P26" t="n">
         <v>-0.01113611787349452</v>
       </c>
-      <c r="N26" t="n">
+      <c r="Q26" t="n">
         <v>3.284615749884662e-15</v>
       </c>
-      <c r="O26" t="n">
+      <c r="R26" t="n">
         <v>-0.009998568475415982</v>
       </c>
-      <c r="P26" t="n">
+      <c r="S26" t="n">
         <v>-9.957497490218503e-17</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="T26" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
         <v>-8.795874158562031e-16</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>3.28462098894533e-15</v>
       </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
         <v>0.01113611787350202</v>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>-0.009998568475415992</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
         <v>-0.001222599374437406</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Z26" t="n">
         <v>9.957666828069171e-17</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
         <v>-8.802264234440092e-16</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>3.284615749884662e-15</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AC26" t="n">
         <v>0.01113611787349452</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AD26" t="n">
         <v>-0.009998568475415982</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AE26" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AF26" t="n">
         <v>9.957497490218503e-17</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AG26" t="n">
         <v>-8.795874158562031e-16</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AH26" t="n">
         <v>6.208286892050575e-16</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AI26" t="n">
         <v>4.729550084903167e-14</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AJ26" t="n">
         <v>-8.408064744864054e-14</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AK26" t="n">
         <v>-4.566659550508945e-16</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AL26" t="n">
         <v>3.361255407452572e-13</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AM26" t="n">
         <v>1.891820033961267e-13</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AN26" t="n">
         <v>-6.208286892050575e-16</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AO26" t="n">
         <v>-4.729550084903167e-14</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AP26" t="n">
         <v>8.408064744864054e-14</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AQ26" t="n">
         <v>4.566659550508945e-16</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AR26" t="n">
         <v>3.356314604241669e-13</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AS26" t="n">
         <v>1.891820033961267e-13</v>
       </c>
     </row>
@@ -5949,127 +7451,138 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>14</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>15</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
+        <v>-1.734723475976807e-18</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.168404344971009e-19</v>
+      </c>
+      <c r="H27" t="n">
         <v>-2.055647319032516e-13</v>
       </c>
-      <c r="F27" t="n">
+      <c r="I27" t="n">
         <v>-4.336808689942018e-11</v>
       </c>
-      <c r="G27" t="n">
+      <c r="J27" t="n">
         <v>-0.01113611787349452</v>
       </c>
-      <c r="H27" t="n">
+      <c r="K27" t="n">
         <v>3.284615749884662e-15</v>
       </c>
-      <c r="I27" t="n">
+      <c r="L27" t="n">
         <v>-0.009998568475415982</v>
       </c>
-      <c r="J27" t="n">
+      <c r="M27" t="n">
         <v>-9.957497490218503e-17</v>
       </c>
-      <c r="K27" t="n">
+      <c r="N27" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="L27" t="n">
+      <c r="O27" t="n">
         <v>-8.795874158562031e-16</v>
       </c>
-      <c r="M27" t="n">
+      <c r="P27" t="n">
         <v>-0.01113611787349453</v>
       </c>
-      <c r="N27" t="n">
+      <c r="Q27" t="n">
         <v>-3.304815612337873e-15</v>
       </c>
-      <c r="O27" t="n">
+      <c r="R27" t="n">
         <v>-1.431524584014678e-06</v>
       </c>
-      <c r="P27" t="n">
+      <c r="S27" t="n">
         <v>1.007394783138497e-16</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="T27" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
         <v>-8.801109181113563e-16</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>-0.01113611787349452</v>
       </c>
-      <c r="T27" t="n">
+      <c r="W27" t="n">
         <v>3.284615749884662e-15</v>
       </c>
-      <c r="U27" t="n">
+      <c r="X27" t="n">
         <v>-0.009998568475415982</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>-9.957497490218503e-17</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AA27" t="n">
         <v>-8.795874158562031e-16</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
         <v>-0.01113611787349453</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AC27" t="n">
         <v>-3.304815612337873e-15</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AD27" t="n">
         <v>-1.431524584014678e-06</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AE27" t="n">
         <v>1.007394783138497e-16</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AF27" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AG27" t="n">
         <v>-8.801109181113563e-16</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AH27" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AI27" t="n">
         <v>-4.676173038271414e-14</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AJ27" t="n">
         <v>-0.02251308472698921</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AK27" t="n">
         <v>-4.275943135957665e-16</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AL27" t="n">
         <v>0.09005233890795705</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AM27" t="n">
         <v>-1.867563777792461e-13</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AN27" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AO27" t="n">
         <v>4.676173038271414e-14</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AP27" t="n">
         <v>0.02251308472698921</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AQ27" t="n">
         <v>4.275943135957665e-16</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AR27" t="n">
         <v>0.09005233890795727</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AS27" t="n">
         <v>-1.87337465282466e-13</v>
       </c>
     </row>
@@ -6077,127 +7590,138 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>15</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>16</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
+        <v>2.271685965345289e-21</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.839607456681611e-22</v>
+      </c>
+      <c r="H28" t="n">
         <v>2.691947868934167e-16</v>
       </c>
-      <c r="F28" t="n">
+      <c r="I28" t="n">
         <v>5.679214913363221e-14</v>
       </c>
-      <c r="G28" t="n">
+      <c r="J28" t="n">
         <v>-0.01113611787349453</v>
       </c>
-      <c r="H28" t="n">
+      <c r="K28" t="n">
         <v>-3.304815612337873e-15</v>
       </c>
-      <c r="I28" t="n">
+      <c r="L28" t="n">
         <v>-1.431524584014678e-06</v>
       </c>
-      <c r="J28" t="n">
+      <c r="M28" t="n">
         <v>1.007394783138497e-16</v>
       </c>
-      <c r="K28" t="n">
+      <c r="N28" t="n">
         <v>-0.001222599374437192</v>
       </c>
-      <c r="L28" t="n">
+      <c r="O28" t="n">
         <v>-8.801109181113563e-16</v>
       </c>
-      <c r="M28" t="n">
+      <c r="P28" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="N28" t="n">
+      <c r="Q28" t="n">
         <v>-3.304817884023839e-15</v>
       </c>
-      <c r="O28" t="n">
+      <c r="R28" t="n">
         <v>-1.43152458401435e-06</v>
       </c>
-      <c r="P28" t="n">
+      <c r="S28" t="n">
         <v>1.007901242459449e-16</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="T28" t="n">
         <v>-0.001222599374437407</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
         <v>-8.800237745202832e-16</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>3.304815612337873e-15</v>
       </c>
-      <c r="T28" t="n">
+      <c r="W28" t="n">
         <v>-0.01113611787349453</v>
       </c>
-      <c r="U28" t="n">
+      <c r="X28" t="n">
         <v>-1.431524584014678e-06</v>
       </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
         <v>0.001222599374437192</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Z28" t="n">
         <v>1.007394783138497e-16</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AA28" t="n">
         <v>-8.801109181113563e-16</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AB28" t="n">
         <v>3.304817884023839e-15</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AC28" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AD28" t="n">
         <v>-1.43152458401435e-06</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AE28" t="n">
         <v>0.001222599374437407</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AF28" t="n">
         <v>1.007901242459449e-16</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AG28" t="n">
         <v>-8.800237745202832e-16</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AH28" t="n">
         <v>-2.691947868883633e-16</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AI28" t="n">
         <v>4.662936703425657e-14</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AJ28" t="n">
         <v>-8.392083454423743e-14</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AK28" t="n">
         <v>-4.597017211338539e-16</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AL28" t="n">
         <v>3.356551736916173e-13</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AM28" t="n">
         <v>1.865174681370263e-13</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AN28" t="n">
         <v>2.691947868883633e-16</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AO28" t="n">
         <v>-4.662936703425657e-14</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AP28" t="n">
         <v>8.392083454423743e-14</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AQ28" t="n">
         <v>4.597017211338539e-16</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AR28" t="n">
         <v>3.357113942420649e-13</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AS28" t="n">
         <v>1.865174681370263e-13</v>
       </c>
     </row>
@@ -6205,127 +7729,138 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>16</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>13</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>8</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
+        <v>1.734723475976807e-18</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.168404344971009e-19</v>
+      </c>
+      <c r="H29" t="n">
         <v>2.055647319032516e-13</v>
       </c>
-      <c r="F29" t="n">
+      <c r="I29" t="n">
         <v>4.336808689942018e-11</v>
       </c>
-      <c r="G29" t="n">
+      <c r="J29" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="H29" t="n">
+      <c r="K29" t="n">
         <v>-3.304817884023839e-15</v>
       </c>
-      <c r="I29" t="n">
+      <c r="L29" t="n">
         <v>-1.43152458401435e-06</v>
       </c>
-      <c r="J29" t="n">
+      <c r="M29" t="n">
         <v>1.007901242459449e-16</v>
       </c>
-      <c r="K29" t="n">
+      <c r="N29" t="n">
         <v>-0.001222599374437407</v>
       </c>
-      <c r="L29" t="n">
+      <c r="O29" t="n">
         <v>-8.800237745202832e-16</v>
       </c>
-      <c r="M29" t="n">
+      <c r="P29" t="n">
         <v>-0.01113611787350202</v>
       </c>
-      <c r="N29" t="n">
+      <c r="Q29" t="n">
         <v>3.28462098894533e-15</v>
       </c>
-      <c r="O29" t="n">
+      <c r="R29" t="n">
         <v>-0.009998568475415992</v>
       </c>
-      <c r="P29" t="n">
+      <c r="S29" t="n">
         <v>-9.957666828069171e-17</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="T29" t="n">
         <v>-0.001222599374437406</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>-8.802264234440092e-16</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>0.01113611787350202</v>
       </c>
-      <c r="T29" t="n">
+      <c r="W29" t="n">
         <v>-3.304817884023839e-15</v>
       </c>
-      <c r="U29" t="n">
+      <c r="X29" t="n">
         <v>1.43152458401435e-06</v>
       </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
         <v>-1.007901242459449e-16</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Z29" t="n">
         <v>-0.001222599374437407</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AA29" t="n">
         <v>8.800237745202832e-16</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AB29" t="n">
         <v>0.01113611787350202</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AC29" t="n">
         <v>3.28462098894533e-15</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AD29" t="n">
         <v>0.009998568475415992</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AE29" t="n">
         <v>9.957666828069171e-17</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AF29" t="n">
         <v>-0.001222599374437406</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AG29" t="n">
         <v>8.802264234440092e-16</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AH29" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AI29" t="n">
         <v>4.699066218428263e-14</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AJ29" t="n">
         <v>-0.02251308472681168</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AK29" t="n">
         <v>-4.277060378933975e-16</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AL29" t="n">
         <v>0.09005233890724629</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AM29" t="n">
         <v>1.878501785844625e-13</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AN29" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AO29" t="n">
         <v>-4.699066218428263e-14</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AP29" t="n">
         <v>0.02251308472681168</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AQ29" t="n">
         <v>4.277060378933975e-16</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AR29" t="n">
         <v>0.09005233890724762</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AS29" t="n">
         <v>1.880751188897983e-13</v>
       </c>
     </row>
@@ -6333,127 +7868,138 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>17</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>18</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
+        <v>1.521452776224584e-21</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.90181597028073e-22</v>
+      </c>
+      <c r="H30" t="n">
         <v>1.802921539826132e-16</v>
       </c>
-      <c r="F30" t="n">
+      <c r="I30" t="n">
         <v>3.80363194056146e-14</v>
       </c>
-      <c r="G30" t="n">
+      <c r="J30" t="n">
         <v>-0.01853807587190909</v>
       </c>
-      <c r="H30" t="n">
+      <c r="K30" t="n">
         <v>3.845064052013146e-15</v>
       </c>
-      <c r="I30" t="n">
+      <c r="L30" t="n">
         <v>-0.009998542574732278</v>
       </c>
-      <c r="J30" t="n">
+      <c r="M30" t="n">
         <v>-4.180501003454598e-17</v>
       </c>
-      <c r="K30" t="n">
+      <c r="N30" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="L30" t="n">
+      <c r="O30" t="n">
         <v>-1.003618666593276e-15</v>
       </c>
-      <c r="M30" t="n">
+      <c r="P30" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="N30" t="n">
+      <c r="Q30" t="n">
         <v>3.845065573465923e-15</v>
       </c>
-      <c r="O30" t="n">
+      <c r="R30" t="n">
         <v>-0.009998542574732268</v>
       </c>
-      <c r="P30" t="n">
+      <c r="S30" t="n">
         <v>-4.187830652248113e-17</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="T30" t="n">
         <v>-0.001244719958365369</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>-1.005467541231768e-15</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>3.845064052013146e-15</v>
       </c>
-      <c r="T30" t="n">
+      <c r="W30" t="n">
         <v>0.01853807587190909</v>
       </c>
-      <c r="U30" t="n">
+      <c r="X30" t="n">
         <v>-0.009998542574732278</v>
       </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Z30" t="n">
         <v>4.180501003454598e-17</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AA30" t="n">
         <v>-1.003618666593276e-15</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AB30" t="n">
         <v>3.845065573465923e-15</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AC30" t="n">
         <v>0.01853807587190073</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AD30" t="n">
         <v>-0.009998542574732268</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AE30" t="n">
         <v>-0.001244719958365369</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AF30" t="n">
         <v>4.187830652248113e-17</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AG30" t="n">
         <v>-1.005467541231768e-15</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AH30" t="n">
         <v>-1.802921540148587e-16</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AI30" t="n">
         <v>3.308464613382966e-14</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AJ30" t="n">
         <v>-3.586154729876037e-14</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AK30" t="n">
         <v>-1.071191746415678e-16</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AL30" t="n">
         <v>1.432963679872677e-13</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AM30" t="n">
         <v>1.323385845353187e-13</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AN30" t="n">
         <v>1.802921540148587e-16</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AO30" t="n">
         <v>-3.308464613382966e-14</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AP30" t="n">
         <v>3.586154729876037e-14</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AQ30" t="n">
         <v>1.071191746415678e-16</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AR30" t="n">
         <v>1.435960104028153e-13</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AS30" t="n">
         <v>1.314504061156185e-13</v>
       </c>
     </row>
@@ -6461,127 +8007,138 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>18</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>19</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="H31" t="n">
+      <c r="K31" t="n">
         <v>3.845065573465923e-15</v>
       </c>
-      <c r="I31" t="n">
+      <c r="L31" t="n">
         <v>-0.009998542574732268</v>
       </c>
-      <c r="J31" t="n">
+      <c r="M31" t="n">
         <v>-4.187830652248113e-17</v>
       </c>
-      <c r="K31" t="n">
+      <c r="N31" t="n">
         <v>-0.001244719958365369</v>
       </c>
-      <c r="L31" t="n">
+      <c r="O31" t="n">
         <v>-1.005467541231768e-15</v>
       </c>
-      <c r="M31" t="n">
+      <c r="P31" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="N31" t="n">
+      <c r="Q31" t="n">
         <v>-3.870980034180524e-15</v>
       </c>
-      <c r="O31" t="n">
+      <c r="R31" t="n">
         <v>-1.457425267729539e-06</v>
       </c>
-      <c r="P31" t="n">
+      <c r="S31" t="n">
         <v>4.302749958412686e-17</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="T31" t="n">
         <v>-0.001244719958365368</v>
       </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>-1.004357076261401e-15</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="T31" t="n">
+      <c r="W31" t="n">
         <v>3.845065573465923e-15</v>
       </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
         <v>-0.009998542574732268</v>
       </c>
-      <c r="V31" t="n">
+      <c r="Y31" t="n">
         <v>-4.187830652248113e-17</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Z31" t="n">
         <v>-0.001244719958365369</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AA31" t="n">
         <v>-1.005467541231768e-15</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AB31" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AC31" t="n">
         <v>-3.870980034180524e-15</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AD31" t="n">
         <v>-1.457425267729539e-06</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AE31" t="n">
         <v>4.302749958412686e-17</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AF31" t="n">
         <v>-0.001244719958365368</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AG31" t="n">
         <v>-1.004357076261401e-15</v>
       </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>-3.363850098582328e-14</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AJ31" t="n">
         <v>-0.004092308026984459</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AK31" t="n">
         <v>-1.812412399583363e-16</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AL31" t="n">
         <v>0.01636923210793761</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AM31" t="n">
         <v>-1.351703120018463e-13</v>
       </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
         <v>3.363850098582328e-14</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AP31" t="n">
         <v>0.004092308026984459</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AQ31" t="n">
         <v>1.812412399583363e-16</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AR31" t="n">
         <v>0.01636923210793872</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AS31" t="n">
         <v>-1.339376958847387e-13</v>
       </c>
     </row>
@@ -6589,127 +8146,138 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>19</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>20</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>8</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
+        <v>-5.267053248582775e-21</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-6.583816560728468e-22</v>
+      </c>
+      <c r="H32" t="n">
         <v>-6.241458099570588e-16</v>
       </c>
-      <c r="F32" t="n">
+      <c r="I32" t="n">
         <v>-1.316763312145694e-13</v>
       </c>
-      <c r="G32" t="n">
+      <c r="J32" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="H32" t="n">
+      <c r="K32" t="n">
         <v>-3.870980034180524e-15</v>
       </c>
-      <c r="I32" t="n">
+      <c r="L32" t="n">
         <v>-1.457425267729539e-06</v>
       </c>
-      <c r="J32" t="n">
+      <c r="M32" t="n">
         <v>4.302749958412686e-17</v>
       </c>
-      <c r="K32" t="n">
+      <c r="N32" t="n">
         <v>-0.001244719958365368</v>
       </c>
-      <c r="L32" t="n">
+      <c r="O32" t="n">
         <v>-1.004357076261401e-15</v>
       </c>
-      <c r="M32" t="n">
+      <c r="P32" t="n">
         <v>-0.01853807587190909</v>
       </c>
-      <c r="N32" t="n">
+      <c r="Q32" t="n">
         <v>-3.870974767127275e-15</v>
       </c>
-      <c r="O32" t="n">
+      <c r="R32" t="n">
         <v>-1.457425267729414e-06</v>
       </c>
-      <c r="P32" t="n">
+      <c r="S32" t="n">
         <v>4.277158646686195e-17</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="T32" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
         <v>-1.004678364397376e-15</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>3.870980034180524e-15</v>
       </c>
-      <c r="T32" t="n">
+      <c r="W32" t="n">
         <v>-0.01853807587190073</v>
       </c>
-      <c r="U32" t="n">
+      <c r="X32" t="n">
         <v>-1.457425267729539e-06</v>
       </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
         <v>0.001244719958365368</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Z32" t="n">
         <v>4.302749958412686e-17</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AA32" t="n">
         <v>-1.004357076261401e-15</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AB32" t="n">
         <v>3.870974767127275e-15</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AC32" t="n">
         <v>-0.01853807587190909</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AD32" t="n">
         <v>-1.457425267729414e-06</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AE32" t="n">
         <v>0.001244719958365419</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AF32" t="n">
         <v>4.277158646686195e-17</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AG32" t="n">
         <v>-1.004678364397376e-15</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AH32" t="n">
         <v>6.241458099166313e-16</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AI32" t="n">
         <v>3.352873534367973e-14</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AJ32" t="n">
         <v>-3.572678161051504e-14</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AK32" t="n">
         <v>-1.101549407245273e-16</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AL32" t="n">
         <v>1.430490993232485e-13</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AM32" t="n">
         <v>1.341149413747189e-13</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AN32" t="n">
         <v>-6.241458099166313e-16</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AO32" t="n">
         <v>-3.352873534367973e-14</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AP32" t="n">
         <v>3.572678161051504e-14</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AQ32" t="n">
         <v>1.101549407245273e-16</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AR32" t="n">
         <v>1.427650451406545e-13</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AS32" t="n">
         <v>1.341149413747189e-13</v>
       </c>
     </row>
@@ -6717,127 +8285,138 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>20</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>17</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>8</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
+        <v>-3.469446951953614e-18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-4.336808689942018e-19</v>
+      </c>
+      <c r="H33" t="n">
         <v>-4.111294638065033e-13</v>
       </c>
-      <c r="F33" t="n">
+      <c r="I33" t="n">
         <v>-8.673617379884035e-11</v>
       </c>
-      <c r="G33" t="n">
+      <c r="J33" t="n">
         <v>-0.01853807587190909</v>
       </c>
-      <c r="H33" t="n">
+      <c r="K33" t="n">
         <v>-3.870974767127275e-15</v>
       </c>
-      <c r="I33" t="n">
+      <c r="L33" t="n">
         <v>-1.457425267729414e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="M33" t="n">
         <v>4.277158646686195e-17</v>
       </c>
-      <c r="K33" t="n">
+      <c r="N33" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="L33" t="n">
+      <c r="O33" t="n">
         <v>-1.004678364397376e-15</v>
       </c>
-      <c r="M33" t="n">
+      <c r="P33" t="n">
         <v>-0.01853807587190909</v>
       </c>
-      <c r="N33" t="n">
+      <c r="Q33" t="n">
         <v>3.845064052013146e-15</v>
       </c>
-      <c r="O33" t="n">
+      <c r="R33" t="n">
         <v>-0.009998542574732278</v>
       </c>
-      <c r="P33" t="n">
+      <c r="S33" t="n">
         <v>-4.180501003454598e-17</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="T33" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
         <v>-1.003618666593276e-15</v>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
         <v>0.01853807587190909</v>
       </c>
-      <c r="T33" t="n">
+      <c r="W33" t="n">
         <v>-3.870974767127275e-15</v>
       </c>
-      <c r="U33" t="n">
+      <c r="X33" t="n">
         <v>1.457425267729414e-06</v>
       </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
         <v>-4.277158646686195e-17</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Z33" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AA33" t="n">
         <v>1.004678364397376e-15</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AB33" t="n">
         <v>0.01853807587190909</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AC33" t="n">
         <v>3.845064052013146e-15</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AD33" t="n">
         <v>0.009998542574732278</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AE33" t="n">
         <v>4.180501003454598e-17</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AF33" t="n">
         <v>-0.001244719958365419</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AG33" t="n">
         <v>1.003618666593276e-15</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AH33" t="n">
         <v>4.547473508864641e-13</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AI33" t="n">
         <v>3.300334953305864e-14</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AJ33" t="n">
         <v>-0.004092308026943159</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AK33" t="n">
         <v>-1.805385040703131e-16</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AL33" t="n">
         <v>0.0163692321077733</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AM33" t="n">
         <v>1.326015304135093e-13</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AN33" t="n">
         <v>-4.547473508864641e-13</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AO33" t="n">
         <v>-3.300334953305864e-14</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AP33" t="n">
         <v>0.004092308026943159</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AQ33" t="n">
         <v>1.805385040703131e-16</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AR33" t="n">
         <v>0.01636923210777352</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AS33" t="n">
         <v>1.314252658509586e-13</v>
       </c>
     </row>
